--- a/web_design_forms/003_logo_design_competition_form--web_design_forms.xlsx
+++ b/web_design_forms/003_logo_design_competition_form--web_design_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1106,8 +1106,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="36" customWidth="1" min="1" max="1"/>
-    <col width="31" customWidth="1" min="2" max="2"/>
-    <col width="31" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1135,12 +1135,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'label':_'vector'}</t>
+          <t>vector</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'label': 'Vector'}</t>
+          <t>Vector</t>
         </is>
       </c>
     </row>
@@ -1152,12 +1152,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'label':_'raster'}</t>
+          <t>raster</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'label': 'Raster'}</t>
+          <t>Raster</t>
         </is>
       </c>
     </row>
@@ -1169,12 +1169,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'label':_'vector_or_raster'}</t>
+          <t>vector_or_raster</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'label': 'Vector or Raster'}</t>
+          <t>Vector or Raster</t>
         </is>
       </c>
     </row>
@@ -1186,12 +1186,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'label':_'monochromatic'}</t>
+          <t>monochromatic</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'label': 'Monochromatic'}</t>
+          <t>Monochromatic</t>
         </is>
       </c>
     </row>
@@ -1203,12 +1203,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'label':_'bicolor'}</t>
+          <t>bicolor</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'label': 'Bicolor'}</t>
+          <t>Bicolor</t>
         </is>
       </c>
     </row>
@@ -1220,12 +1220,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'label':_'tricolor'}</t>
+          <t>tricolor</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'label': 'Tricolor'}</t>
+          <t>Tricolor</t>
         </is>
       </c>
     </row>
@@ -1237,12 +1237,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'label':_'i_agree'}</t>
+          <t>i_agree</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'label': 'I Agree'}</t>
+          <t>I Agree</t>
         </is>
       </c>
     </row>
@@ -1254,12 +1254,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'label':_'i_disagree'}</t>
+          <t>i_disagree</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'label': 'I Disagree'}</t>
+          <t>I Disagree</t>
         </is>
       </c>
     </row>
@@ -1271,12 +1271,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'label':_'web'}</t>
+          <t>web</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'label': 'Web'}</t>
+          <t>Web</t>
         </is>
       </c>
     </row>
@@ -1288,12 +1288,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'label':_'graphics'}</t>
+          <t>graphics</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'label': 'Graphics'}</t>
+          <t>Graphics</t>
         </is>
       </c>
     </row>
@@ -1373,12 +1373,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'label':_'not_started'}</t>
+          <t>not_started</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'label': 'Not Started'}</t>
+          <t>Not Started</t>
         </is>
       </c>
     </row>
@@ -1390,12 +1390,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'label':_'in_progress'}</t>
+          <t>in_progress</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'label': 'In Progress'}</t>
+          <t>In Progress</t>
         </is>
       </c>
     </row>
@@ -1407,12 +1407,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'label':_'completed'}</t>
+          <t>completed</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'label': 'Completed'}</t>
+          <t>Completed</t>
         </is>
       </c>
     </row>
@@ -1424,12 +1424,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'label':_'cancelled'}</t>
+          <t>cancelled</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'label': 'Cancelled'}</t>
+          <t>Cancelled</t>
         </is>
       </c>
     </row>
@@ -1441,12 +1441,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'label':_'not_started'}</t>
+          <t>not_started</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'label': 'Not Started'}</t>
+          <t>Not Started</t>
         </is>
       </c>
     </row>
@@ -1458,12 +1458,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>{'label':_'in_progress'}</t>
+          <t>in_progress</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>{'label': 'In Progress'}</t>
+          <t>In Progress</t>
         </is>
       </c>
     </row>
@@ -1475,12 +1475,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>{'label':_'completed'}</t>
+          <t>completed</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>{'label': 'Completed'}</t>
+          <t>Completed</t>
         </is>
       </c>
     </row>
@@ -1492,12 +1492,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>{'label':_'cancelled'}</t>
+          <t>cancelled</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>{'label': 'Cancelled'}</t>
+          <t>Cancelled</t>
         </is>
       </c>
     </row>
